--- a/data/processed/tabela_partidas_tratada.xlsx
+++ b/data/processed/tabela_partidas_tratada.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -530,7 +530,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -575,7 +575,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -583,7 +583,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>POSTPONED</t>
+          <t>ADIADO</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L141" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>VISITANTE</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>FINISHED</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>MANDANTE</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J242" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J251" t="n">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J252" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J253" t="n">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J254" t="n">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J255" t="n">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J256" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J257" t="n">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J258" t="n">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J259" t="n">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J260" t="n">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J261" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J262" t="n">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J263" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J264" t="n">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J265" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J266" t="n">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J267" t="n">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J268" t="n">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J269" t="n">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J270" t="n">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J273" t="n">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J274" t="n">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J275" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J276" t="n">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J277" t="n">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J278" t="n">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J279" t="n">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J280" t="n">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J281" t="n">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J282" t="n">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J283" t="n">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J284" t="n">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J285" t="n">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J286" t="n">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J287" t="n">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J288" t="n">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J289" t="n">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J290" t="n">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J291" t="n">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J292" t="n">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J293" t="n">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J294" t="n">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J295" t="n">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J296" t="n">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J297" t="n">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J298" t="n">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J299" t="n">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J300" t="n">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J301" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J302" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J303" t="n">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J304" t="n">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J305" t="n">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J306" t="n">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J307" t="n">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J308" t="n">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J309" t="n">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J310" t="n">
@@ -14989,7 +14989,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J311" t="n">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J312" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J313" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J314" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J315" t="n">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J316" t="n">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J317" t="n">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J318" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J319" t="n">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J320" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J321" t="n">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J322" t="n">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J323" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J324" t="n">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J325" t="n">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J326" t="n">
@@ -15613,7 +15613,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J327" t="n">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J328" t="n">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J329" t="n">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J330" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J331" t="n">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J332" t="n">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J333" t="n">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J334" t="n">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J335" t="n">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J336" t="n">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J337" t="n">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J338" t="n">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J339" t="n">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J340" t="n">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J341" t="n">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J342" t="n">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J343" t="n">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J344" t="n">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J345" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J346" t="n">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J347" t="n">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J348" t="n">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J349" t="n">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J350" t="n">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J351" t="n">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J352" t="n">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J353" t="n">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J354" t="n">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J355" t="n">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J356" t="n">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J357" t="n">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J358" t="n">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J359" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J360" t="n">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J361" t="n">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J362" t="n">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J363" t="n">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J364" t="n">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J365" t="n">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J366" t="n">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J367" t="n">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J368" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J369" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J370" t="n">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J371" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J372" t="n">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J373" t="n">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J374" t="n">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J375" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J376" t="n">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J377" t="n">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J378" t="n">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J379" t="n">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J380" t="n">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>SCHEDULED</t>
+          <t>AGENDADO</t>
         </is>
       </c>
       <c r="J381" t="n">

--- a/data/processed/tabela_partidas_tratada.xlsx
+++ b/data/processed/tabela_partidas_tratada.xlsx
@@ -417,28 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O178"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id_partida</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id_competicao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id_temporada</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>id_area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id_competicao</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id_temporada</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id_partida</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -499,7 +499,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2032</v>
+        <v>554740</v>
       </c>
       <c r="B2" t="n">
         <v>2013</v>
@@ -508,7 +508,7 @@
         <v>2474</v>
       </c>
       <c r="D2" t="n">
-        <v>554740</v>
+        <v>2032</v>
       </c>
       <c r="E2" t="n">
         <v>1766</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2032</v>
+        <v>554744</v>
       </c>
       <c r="B3" t="n">
         <v>2013</v>
@@ -559,7 +559,7 @@
         <v>2474</v>
       </c>
       <c r="D3" t="n">
-        <v>554744</v>
+        <v>2032</v>
       </c>
       <c r="E3" t="n">
         <v>4241</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2032</v>
+        <v>554746</v>
       </c>
       <c r="B4" t="n">
         <v>2013</v>
@@ -610,7 +610,7 @@
         <v>2474</v>
       </c>
       <c r="D4" t="n">
-        <v>554746</v>
+        <v>2032</v>
       </c>
       <c r="E4" t="n">
         <v>6684</v>
@@ -652,7 +652,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2032</v>
+        <v>554749</v>
       </c>
       <c r="B5" t="n">
         <v>2013</v>
@@ -661,7 +661,7 @@
         <v>2474</v>
       </c>
       <c r="D5" t="n">
-        <v>554749</v>
+        <v>2032</v>
       </c>
       <c r="E5" t="n">
         <v>1782</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2032</v>
+        <v>554745</v>
       </c>
       <c r="B6" t="n">
         <v>2013</v>
@@ -712,7 +712,7 @@
         <v>2474</v>
       </c>
       <c r="D6" t="n">
-        <v>554745</v>
+        <v>2032</v>
       </c>
       <c r="E6" t="n">
         <v>1765</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2032</v>
+        <v>554742</v>
       </c>
       <c r="B7" t="n">
         <v>2013</v>
@@ -763,7 +763,7 @@
         <v>2474</v>
       </c>
       <c r="D7" t="n">
-        <v>554742</v>
+        <v>2032</v>
       </c>
       <c r="E7" t="n">
         <v>1772</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2032</v>
+        <v>554743</v>
       </c>
       <c r="B8" t="n">
         <v>2013</v>
@@ -814,7 +814,7 @@
         <v>2474</v>
       </c>
       <c r="D8" t="n">
-        <v>554743</v>
+        <v>2032</v>
       </c>
       <c r="E8" t="n">
         <v>1779</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2032</v>
+        <v>554748</v>
       </c>
       <c r="B9" t="n">
         <v>2013</v>
@@ -865,7 +865,7 @@
         <v>2474</v>
       </c>
       <c r="D9" t="n">
-        <v>554748</v>
+        <v>2032</v>
       </c>
       <c r="E9" t="n">
         <v>1776</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2032</v>
+        <v>554747</v>
       </c>
       <c r="B10" t="n">
         <v>2013</v>
@@ -916,7 +916,7 @@
         <v>2474</v>
       </c>
       <c r="D10" t="n">
-        <v>554747</v>
+        <v>2032</v>
       </c>
       <c r="E10" t="n">
         <v>4364</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2032</v>
+        <v>554741</v>
       </c>
       <c r="B11" t="n">
         <v>2013</v>
@@ -967,7 +967,7 @@
         <v>2474</v>
       </c>
       <c r="D11" t="n">
-        <v>554741</v>
+        <v>2032</v>
       </c>
       <c r="E11" t="n">
         <v>1770</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2032</v>
+        <v>554752</v>
       </c>
       <c r="B12" t="n">
         <v>2013</v>
@@ -1018,7 +1018,7 @@
         <v>2474</v>
       </c>
       <c r="D12" t="n">
-        <v>554752</v>
+        <v>2032</v>
       </c>
       <c r="E12" t="n">
         <v>4286</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2032</v>
+        <v>554754</v>
       </c>
       <c r="B13" t="n">
         <v>2013</v>
@@ -1069,7 +1069,7 @@
         <v>2474</v>
       </c>
       <c r="D13" t="n">
-        <v>554754</v>
+        <v>2032</v>
       </c>
       <c r="E13" t="n">
         <v>1783</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2032</v>
+        <v>554757</v>
       </c>
       <c r="B14" t="n">
         <v>2013</v>
@@ -1120,7 +1120,7 @@
         <v>2474</v>
       </c>
       <c r="D14" t="n">
-        <v>554757</v>
+        <v>2032</v>
       </c>
       <c r="E14" t="n">
         <v>4287</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2032</v>
+        <v>554758</v>
       </c>
       <c r="B15" t="n">
         <v>2013</v>
@@ -1171,7 +1171,7 @@
         <v>2474</v>
       </c>
       <c r="D15" t="n">
-        <v>554758</v>
+        <v>2032</v>
       </c>
       <c r="E15" t="n">
         <v>6685</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2032</v>
+        <v>554755</v>
       </c>
       <c r="B16" t="n">
         <v>2013</v>
@@ -1222,7 +1222,7 @@
         <v>2474</v>
       </c>
       <c r="D16" t="n">
-        <v>554755</v>
+        <v>2032</v>
       </c>
       <c r="E16" t="n">
         <v>1767</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2032</v>
+        <v>554756</v>
       </c>
       <c r="B17" t="n">
         <v>2013</v>
@@ -1273,7 +1273,7 @@
         <v>2474</v>
       </c>
       <c r="D17" t="n">
-        <v>554756</v>
+        <v>2032</v>
       </c>
       <c r="E17" t="n">
         <v>1769</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2032</v>
+        <v>554751</v>
       </c>
       <c r="B18" t="n">
         <v>2013</v>
@@ -1324,7 +1324,7 @@
         <v>2474</v>
       </c>
       <c r="D18" t="n">
-        <v>554751</v>
+        <v>2032</v>
       </c>
       <c r="E18" t="n">
         <v>1777</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2032</v>
+        <v>554759</v>
       </c>
       <c r="B19" t="n">
         <v>2013</v>
@@ -1375,7 +1375,7 @@
         <v>2474</v>
       </c>
       <c r="D19" t="n">
-        <v>554759</v>
+        <v>2032</v>
       </c>
       <c r="E19" t="n">
         <v>1780</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2032</v>
+        <v>554753</v>
       </c>
       <c r="B20" t="n">
         <v>2013</v>
@@ -1426,7 +1426,7 @@
         <v>2474</v>
       </c>
       <c r="D20" t="n">
-        <v>554753</v>
+        <v>2032</v>
       </c>
       <c r="E20" t="n">
         <v>1771</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2032</v>
+        <v>554769</v>
       </c>
       <c r="B21" t="n">
         <v>2013</v>
@@ -1477,7 +1477,7 @@
         <v>2474</v>
       </c>
       <c r="D21" t="n">
-        <v>554769</v>
+        <v>2032</v>
       </c>
       <c r="E21" t="n">
         <v>1782</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2032</v>
+        <v>554762</v>
       </c>
       <c r="B22" t="n">
         <v>2013</v>
@@ -1528,7 +1528,7 @@
         <v>2474</v>
       </c>
       <c r="D22" t="n">
-        <v>554762</v>
+        <v>2032</v>
       </c>
       <c r="E22" t="n">
         <v>1772</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2032</v>
+        <v>554766</v>
       </c>
       <c r="B23" t="n">
         <v>2013</v>
@@ -1579,7 +1579,7 @@
         <v>2474</v>
       </c>
       <c r="D23" t="n">
-        <v>554766</v>
+        <v>2032</v>
       </c>
       <c r="E23" t="n">
         <v>4364</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2032</v>
+        <v>554761</v>
       </c>
       <c r="B24" t="n">
         <v>2013</v>
@@ -1630,7 +1630,7 @@
         <v>2474</v>
       </c>
       <c r="D24" t="n">
-        <v>554761</v>
+        <v>2032</v>
       </c>
       <c r="E24" t="n">
         <v>1766</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2032</v>
+        <v>554767</v>
       </c>
       <c r="B25" t="n">
         <v>2013</v>
@@ -1681,7 +1681,7 @@
         <v>2474</v>
       </c>
       <c r="D25" t="n">
-        <v>554767</v>
+        <v>2032</v>
       </c>
       <c r="E25" t="n">
         <v>1776</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2032</v>
+        <v>554768</v>
       </c>
       <c r="B26" t="n">
         <v>2013</v>
@@ -1732,7 +1732,7 @@
         <v>2474</v>
       </c>
       <c r="D26" t="n">
-        <v>554768</v>
+        <v>2032</v>
       </c>
       <c r="E26" t="n">
         <v>1780</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2032</v>
+        <v>554760</v>
       </c>
       <c r="B27" t="n">
         <v>2013</v>
@@ -1783,7 +1783,7 @@
         <v>2474</v>
       </c>
       <c r="D27" t="n">
-        <v>554760</v>
+        <v>2032</v>
       </c>
       <c r="E27" t="n">
         <v>1768</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2032</v>
+        <v>554764</v>
       </c>
       <c r="B28" t="n">
         <v>2013</v>
@@ -1834,7 +1834,7 @@
         <v>2474</v>
       </c>
       <c r="D28" t="n">
-        <v>554764</v>
+        <v>2032</v>
       </c>
       <c r="E28" t="n">
         <v>1765</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2032</v>
+        <v>554763</v>
       </c>
       <c r="B29" t="n">
         <v>2013</v>
@@ -1885,7 +1885,7 @@
         <v>2474</v>
       </c>
       <c r="D29" t="n">
-        <v>554763</v>
+        <v>2032</v>
       </c>
       <c r="E29" t="n">
         <v>1779</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2032</v>
+        <v>554765</v>
       </c>
       <c r="B30" t="n">
         <v>2013</v>
@@ -1936,7 +1936,7 @@
         <v>2474</v>
       </c>
       <c r="D30" t="n">
-        <v>554765</v>
+        <v>2032</v>
       </c>
       <c r="E30" t="n">
         <v>6684</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2032</v>
+        <v>554750</v>
       </c>
       <c r="B31" t="n">
         <v>2013</v>
@@ -1987,7 +1987,7 @@
         <v>2474</v>
       </c>
       <c r="D31" t="n">
-        <v>554750</v>
+        <v>2032</v>
       </c>
       <c r="E31" t="n">
         <v>1768</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2032</v>
+        <v>554772</v>
       </c>
       <c r="B32" t="n">
         <v>2013</v>
@@ -2038,7 +2038,7 @@
         <v>2474</v>
       </c>
       <c r="D32" t="n">
-        <v>554772</v>
+        <v>2032</v>
       </c>
       <c r="E32" t="n">
         <v>4286</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2032</v>
+        <v>554778</v>
       </c>
       <c r="B33" t="n">
         <v>2013</v>
@@ -2089,7 +2089,7 @@
         <v>2474</v>
       </c>
       <c r="D33" t="n">
-        <v>554778</v>
+        <v>2032</v>
       </c>
       <c r="E33" t="n">
         <v>4287</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2032</v>
+        <v>554773</v>
       </c>
       <c r="B34" t="n">
         <v>2013</v>
@@ -2140,7 +2140,7 @@
         <v>2474</v>
       </c>
       <c r="D34" t="n">
-        <v>554773</v>
+        <v>2032</v>
       </c>
       <c r="E34" t="n">
         <v>4241</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2032</v>
+        <v>554774</v>
       </c>
       <c r="B35" t="n">
         <v>2013</v>
@@ -2191,7 +2191,7 @@
         <v>2474</v>
       </c>
       <c r="D35" t="n">
-        <v>554774</v>
+        <v>2032</v>
       </c>
       <c r="E35" t="n">
         <v>1771</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2032</v>
+        <v>554776</v>
       </c>
       <c r="B36" t="n">
         <v>2013</v>
@@ -2242,7 +2242,7 @@
         <v>2474</v>
       </c>
       <c r="D36" t="n">
-        <v>554776</v>
+        <v>2032</v>
       </c>
       <c r="E36" t="n">
         <v>1767</v>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2032</v>
+        <v>554777</v>
       </c>
       <c r="B37" t="n">
         <v>2013</v>
@@ -2293,7 +2293,7 @@
         <v>2474</v>
       </c>
       <c r="D37" t="n">
-        <v>554777</v>
+        <v>2032</v>
       </c>
       <c r="E37" t="n">
         <v>1769</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2032</v>
+        <v>554779</v>
       </c>
       <c r="B38" t="n">
         <v>2013</v>
@@ -2344,7 +2344,7 @@
         <v>2474</v>
       </c>
       <c r="D38" t="n">
-        <v>554779</v>
+        <v>2032</v>
       </c>
       <c r="E38" t="n">
         <v>6685</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2032</v>
+        <v>554786</v>
       </c>
       <c r="B39" t="n">
         <v>2013</v>
@@ -2395,7 +2395,7 @@
         <v>2474</v>
       </c>
       <c r="D39" t="n">
-        <v>554786</v>
+        <v>2032</v>
       </c>
       <c r="E39" t="n">
         <v>4364</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2032</v>
+        <v>554781</v>
       </c>
       <c r="B40" t="n">
         <v>2013</v>
@@ -2446,7 +2446,7 @@
         <v>2474</v>
       </c>
       <c r="D40" t="n">
-        <v>554781</v>
+        <v>2032</v>
       </c>
       <c r="E40" t="n">
         <v>1766</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2032</v>
+        <v>554782</v>
       </c>
       <c r="B41" t="n">
         <v>2013</v>
@@ -2497,7 +2497,7 @@
         <v>2474</v>
       </c>
       <c r="D41" t="n">
-        <v>554782</v>
+        <v>2032</v>
       </c>
       <c r="E41" t="n">
         <v>1777</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2032</v>
+        <v>554783</v>
       </c>
       <c r="B42" t="n">
         <v>2013</v>
@@ -2548,7 +2548,7 @@
         <v>2474</v>
       </c>
       <c r="D42" t="n">
-        <v>554783</v>
+        <v>2032</v>
       </c>
       <c r="E42" t="n">
         <v>1779</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2032</v>
+        <v>554784</v>
       </c>
       <c r="B43" t="n">
         <v>2013</v>
@@ -2599,7 +2599,7 @@
         <v>2474</v>
       </c>
       <c r="D43" t="n">
-        <v>554784</v>
+        <v>2032</v>
       </c>
       <c r="E43" t="n">
         <v>1783</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2032</v>
+        <v>554787</v>
       </c>
       <c r="B44" t="n">
         <v>2013</v>
@@ -2650,7 +2650,7 @@
         <v>2474</v>
       </c>
       <c r="D44" t="n">
-        <v>554787</v>
+        <v>2032</v>
       </c>
       <c r="E44" t="n">
         <v>4287</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2032</v>
+        <v>554789</v>
       </c>
       <c r="B45" t="n">
         <v>2013</v>
@@ -2701,7 +2701,7 @@
         <v>2474</v>
       </c>
       <c r="D45" t="n">
-        <v>554789</v>
+        <v>2032</v>
       </c>
       <c r="E45" t="n">
         <v>1780</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2032</v>
+        <v>554788</v>
       </c>
       <c r="B46" t="n">
         <v>2013</v>
@@ -2752,7 +2752,7 @@
         <v>2474</v>
       </c>
       <c r="D46" t="n">
-        <v>554788</v>
+        <v>2032</v>
       </c>
       <c r="E46" t="n">
         <v>1776</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2032</v>
+        <v>554785</v>
       </c>
       <c r="B47" t="n">
         <v>2013</v>
@@ -2803,7 +2803,7 @@
         <v>2474</v>
       </c>
       <c r="D47" t="n">
-        <v>554785</v>
+        <v>2032</v>
       </c>
       <c r="E47" t="n">
         <v>1767</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2032</v>
+        <v>554799</v>
       </c>
       <c r="B48" t="n">
         <v>2013</v>
@@ -2854,7 +2854,7 @@
         <v>2474</v>
       </c>
       <c r="D48" t="n">
-        <v>554799</v>
+        <v>2032</v>
       </c>
       <c r="E48" t="n">
         <v>1782</v>
@@ -2896,7 +2896,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2032</v>
+        <v>554790</v>
       </c>
       <c r="B49" t="n">
         <v>2013</v>
@@ -2905,7 +2905,7 @@
         <v>2474</v>
       </c>
       <c r="D49" t="n">
-        <v>554790</v>
+        <v>2032</v>
       </c>
       <c r="E49" t="n">
         <v>1770</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2032</v>
+        <v>554795</v>
       </c>
       <c r="B50" t="n">
         <v>2013</v>
@@ -2956,7 +2956,7 @@
         <v>2474</v>
       </c>
       <c r="D50" t="n">
-        <v>554795</v>
+        <v>2032</v>
       </c>
       <c r="E50" t="n">
         <v>1765</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2032</v>
+        <v>554796</v>
       </c>
       <c r="B51" t="n">
         <v>2013</v>
@@ -3007,7 +3007,7 @@
         <v>2474</v>
       </c>
       <c r="D51" t="n">
-        <v>554796</v>
+        <v>2032</v>
       </c>
       <c r="E51" t="n">
         <v>6684</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2032</v>
+        <v>554798</v>
       </c>
       <c r="B52" t="n">
         <v>2013</v>
@@ -3058,7 +3058,7 @@
         <v>2474</v>
       </c>
       <c r="D52" t="n">
-        <v>554798</v>
+        <v>2032</v>
       </c>
       <c r="E52" t="n">
         <v>6685</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2032</v>
+        <v>554793</v>
       </c>
       <c r="B53" t="n">
         <v>2013</v>
@@ -3109,7 +3109,7 @@
         <v>2474</v>
       </c>
       <c r="D53" t="n">
-        <v>554793</v>
+        <v>2032</v>
       </c>
       <c r="E53" t="n">
         <v>4241</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2032</v>
+        <v>554797</v>
       </c>
       <c r="B54" t="n">
         <v>2013</v>
@@ -3160,7 +3160,7 @@
         <v>2474</v>
       </c>
       <c r="D54" t="n">
-        <v>554797</v>
+        <v>2032</v>
       </c>
       <c r="E54" t="n">
         <v>1769</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2032</v>
+        <v>554791</v>
       </c>
       <c r="B55" t="n">
         <v>2013</v>
@@ -3211,7 +3211,7 @@
         <v>2474</v>
       </c>
       <c r="D55" t="n">
-        <v>554791</v>
+        <v>2032</v>
       </c>
       <c r="E55" t="n">
         <v>4286</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2032</v>
+        <v>554794</v>
       </c>
       <c r="B56" t="n">
         <v>2013</v>
@@ -3262,7 +3262,7 @@
         <v>2474</v>
       </c>
       <c r="D56" t="n">
-        <v>554794</v>
+        <v>2032</v>
       </c>
       <c r="E56" t="n">
         <v>1771</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2032</v>
+        <v>554792</v>
       </c>
       <c r="B57" t="n">
         <v>2013</v>
@@ -3313,7 +3313,7 @@
         <v>2474</v>
       </c>
       <c r="D57" t="n">
-        <v>554792</v>
+        <v>2032</v>
       </c>
       <c r="E57" t="n">
         <v>1772</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2032</v>
+        <v>554802</v>
       </c>
       <c r="B58" t="n">
         <v>2013</v>
@@ -3364,7 +3364,7 @@
         <v>2474</v>
       </c>
       <c r="D58" t="n">
-        <v>554802</v>
+        <v>2032</v>
       </c>
       <c r="E58" t="n">
         <v>1777</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2032</v>
+        <v>554807</v>
       </c>
       <c r="B59" t="n">
         <v>2013</v>
@@ -3415,7 +3415,7 @@
         <v>2474</v>
       </c>
       <c r="D59" t="n">
-        <v>554807</v>
+        <v>2032</v>
       </c>
       <c r="E59" t="n">
         <v>1769</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2032</v>
+        <v>554800</v>
       </c>
       <c r="B60" t="n">
         <v>2013</v>
@@ -3466,7 +3466,7 @@
         <v>2474</v>
       </c>
       <c r="D60" t="n">
-        <v>554800</v>
+        <v>2032</v>
       </c>
       <c r="E60" t="n">
         <v>1768</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2032</v>
+        <v>554801</v>
       </c>
       <c r="B61" t="n">
         <v>2013</v>
@@ -3517,7 +3517,7 @@
         <v>2474</v>
       </c>
       <c r="D61" t="n">
-        <v>554801</v>
+        <v>2032</v>
       </c>
       <c r="E61" t="n">
         <v>1766</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2032</v>
+        <v>554806</v>
       </c>
       <c r="B62" t="n">
         <v>2013</v>
@@ -3568,7 +3568,7 @@
         <v>2474</v>
       </c>
       <c r="D62" t="n">
-        <v>554806</v>
+        <v>2032</v>
       </c>
       <c r="E62" t="n">
         <v>4364</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2032</v>
+        <v>554808</v>
       </c>
       <c r="B63" t="n">
         <v>2013</v>
@@ -3619,7 +3619,7 @@
         <v>2474</v>
       </c>
       <c r="D63" t="n">
-        <v>554808</v>
+        <v>2032</v>
       </c>
       <c r="E63" t="n">
         <v>6685</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2032</v>
+        <v>554809</v>
       </c>
       <c r="B64" t="n">
         <v>2013</v>
@@ -3670,7 +3670,7 @@
         <v>2474</v>
       </c>
       <c r="D64" t="n">
-        <v>554809</v>
+        <v>2032</v>
       </c>
       <c r="E64" t="n">
         <v>1780</v>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2032</v>
+        <v>554805</v>
       </c>
       <c r="B65" t="n">
         <v>2013</v>
@@ -3721,7 +3721,7 @@
         <v>2474</v>
       </c>
       <c r="D65" t="n">
-        <v>554805</v>
+        <v>2032</v>
       </c>
       <c r="E65" t="n">
         <v>1767</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2032</v>
+        <v>554804</v>
       </c>
       <c r="B66" t="n">
         <v>2013</v>
@@ -3772,7 +3772,7 @@
         <v>2474</v>
       </c>
       <c r="D66" t="n">
-        <v>554804</v>
+        <v>2032</v>
       </c>
       <c r="E66" t="n">
         <v>1783</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2032</v>
+        <v>554803</v>
       </c>
       <c r="B67" t="n">
         <v>2013</v>
@@ -3823,7 +3823,7 @@
         <v>2474</v>
       </c>
       <c r="D67" t="n">
-        <v>554803</v>
+        <v>2032</v>
       </c>
       <c r="E67" t="n">
         <v>1772</v>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2032</v>
+        <v>554811</v>
       </c>
       <c r="B68" t="n">
         <v>2013</v>
@@ -3874,7 +3874,7 @@
         <v>2474</v>
       </c>
       <c r="D68" t="n">
-        <v>554811</v>
+        <v>2032</v>
       </c>
       <c r="E68" t="n">
         <v>4286</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2032</v>
+        <v>554814</v>
       </c>
       <c r="B69" t="n">
         <v>2013</v>
@@ -3925,7 +3925,7 @@
         <v>2474</v>
       </c>
       <c r="D69" t="n">
-        <v>554814</v>
+        <v>2032</v>
       </c>
       <c r="E69" t="n">
         <v>1765</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2032</v>
+        <v>554817</v>
       </c>
       <c r="B70" t="n">
         <v>2013</v>
@@ -3976,7 +3976,7 @@
         <v>2474</v>
       </c>
       <c r="D70" t="n">
-        <v>554817</v>
+        <v>2032</v>
       </c>
       <c r="E70" t="n">
         <v>1776</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2032</v>
+        <v>554810</v>
       </c>
       <c r="B71" t="n">
         <v>2013</v>
@@ -4027,7 +4027,7 @@
         <v>2474</v>
       </c>
       <c r="D71" t="n">
-        <v>554810</v>
+        <v>2032</v>
       </c>
       <c r="E71" t="n">
         <v>1768</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2032</v>
+        <v>554813</v>
       </c>
       <c r="B72" t="n">
         <v>2013</v>
@@ -4078,7 +4078,7 @@
         <v>2474</v>
       </c>
       <c r="D72" t="n">
-        <v>554813</v>
+        <v>2032</v>
       </c>
       <c r="E72" t="n">
         <v>1771</v>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2032</v>
+        <v>554816</v>
       </c>
       <c r="B73" t="n">
         <v>2013</v>
@@ -4129,7 +4129,7 @@
         <v>2474</v>
       </c>
       <c r="D73" t="n">
-        <v>554816</v>
+        <v>2032</v>
       </c>
       <c r="E73" t="n">
         <v>4287</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2032</v>
+        <v>554818</v>
       </c>
       <c r="B74" t="n">
         <v>2013</v>
@@ -4180,7 +4180,7 @@
         <v>2474</v>
       </c>
       <c r="D74" t="n">
-        <v>554818</v>
+        <v>2032</v>
       </c>
       <c r="E74" t="n">
         <v>1780</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2032</v>
+        <v>554815</v>
       </c>
       <c r="B75" t="n">
         <v>2013</v>
@@ -4231,7 +4231,7 @@
         <v>2474</v>
       </c>
       <c r="D75" t="n">
-        <v>554815</v>
+        <v>2032</v>
       </c>
       <c r="E75" t="n">
         <v>6684</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2032</v>
+        <v>554819</v>
       </c>
       <c r="B76" t="n">
         <v>2013</v>
@@ -4282,7 +4282,7 @@
         <v>2474</v>
       </c>
       <c r="D76" t="n">
-        <v>554819</v>
+        <v>2032</v>
       </c>
       <c r="E76" t="n">
         <v>1782</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2032</v>
+        <v>554812</v>
       </c>
       <c r="B77" t="n">
         <v>2013</v>
@@ -4333,7 +4333,7 @@
         <v>2474</v>
       </c>
       <c r="D77" t="n">
-        <v>554812</v>
+        <v>2032</v>
       </c>
       <c r="E77" t="n">
         <v>1779</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2032</v>
+        <v>554780</v>
       </c>
       <c r="B78" t="n">
         <v>2013</v>
@@ -4384,7 +4384,7 @@
         <v>2474</v>
       </c>
       <c r="D78" t="n">
-        <v>554780</v>
+        <v>2032</v>
       </c>
       <c r="E78" t="n">
         <v>1768</v>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2032</v>
+        <v>554821</v>
       </c>
       <c r="B79" t="n">
         <v>2013</v>
@@ -4435,7 +4435,7 @@
         <v>2474</v>
       </c>
       <c r="D79" t="n">
-        <v>554821</v>
+        <v>2032</v>
       </c>
       <c r="E79" t="n">
         <v>1770</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2032</v>
+        <v>554827</v>
       </c>
       <c r="B80" t="n">
         <v>2013</v>
@@ -4486,7 +4486,7 @@
         <v>2474</v>
       </c>
       <c r="D80" t="n">
-        <v>554827</v>
+        <v>2032</v>
       </c>
       <c r="E80" t="n">
         <v>6684</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2032</v>
+        <v>554820</v>
       </c>
       <c r="B81" t="n">
         <v>2013</v>
@@ -4537,7 +4537,7 @@
         <v>2474</v>
       </c>
       <c r="D81" t="n">
-        <v>554820</v>
+        <v>2032</v>
       </c>
       <c r="E81" t="n">
         <v>1777</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2032</v>
+        <v>554825</v>
       </c>
       <c r="B82" t="n">
         <v>2013</v>
@@ -4588,7 +4588,7 @@
         <v>2474</v>
       </c>
       <c r="D82" t="n">
-        <v>554825</v>
+        <v>2032</v>
       </c>
       <c r="E82" t="n">
         <v>1771</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2032</v>
+        <v>554824</v>
       </c>
       <c r="B83" t="n">
         <v>2013</v>
@@ -4639,7 +4639,7 @@
         <v>2474</v>
       </c>
       <c r="D83" t="n">
-        <v>554824</v>
+        <v>2032</v>
       </c>
       <c r="E83" t="n">
         <v>4241</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2032</v>
+        <v>554826</v>
       </c>
       <c r="B84" t="n">
         <v>2013</v>
@@ -4690,7 +4690,7 @@
         <v>2474</v>
       </c>
       <c r="D84" t="n">
-        <v>554826</v>
+        <v>2032</v>
       </c>
       <c r="E84" t="n">
         <v>1765</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2032</v>
+        <v>554823</v>
       </c>
       <c r="B85" t="n">
         <v>2013</v>
@@ -4741,7 +4741,7 @@
         <v>2474</v>
       </c>
       <c r="D85" t="n">
-        <v>554823</v>
+        <v>2032</v>
       </c>
       <c r="E85" t="n">
         <v>1772</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2032</v>
+        <v>554829</v>
       </c>
       <c r="B86" t="n">
         <v>2013</v>
@@ -4792,7 +4792,7 @@
         <v>2474</v>
       </c>
       <c r="D86" t="n">
-        <v>554829</v>
+        <v>2032</v>
       </c>
       <c r="E86" t="n">
         <v>6685</v>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2032</v>
+        <v>554822</v>
       </c>
       <c r="B87" t="n">
         <v>2013</v>
@@ -4843,7 +4843,7 @@
         <v>2474</v>
       </c>
       <c r="D87" t="n">
-        <v>554822</v>
+        <v>2032</v>
       </c>
       <c r="E87" t="n">
         <v>4286</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2032</v>
+        <v>554828</v>
       </c>
       <c r="B88" t="n">
         <v>2013</v>
@@ -4894,7 +4894,7 @@
         <v>2474</v>
       </c>
       <c r="D88" t="n">
-        <v>554828</v>
+        <v>2032</v>
       </c>
       <c r="E88" t="n">
         <v>1769</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2032</v>
+        <v>554838</v>
       </c>
       <c r="B89" t="n">
         <v>2013</v>
@@ -4945,7 +4945,7 @@
         <v>2474</v>
       </c>
       <c r="D89" t="n">
-        <v>554838</v>
+        <v>2032</v>
       </c>
       <c r="E89" t="n">
         <v>1776</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2032</v>
+        <v>554834</v>
       </c>
       <c r="B90" t="n">
         <v>2013</v>
@@ -4996,7 +4996,7 @@
         <v>2474</v>
       </c>
       <c r="D90" t="n">
-        <v>554834</v>
+        <v>2032</v>
       </c>
       <c r="E90" t="n">
         <v>4241</v>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2032</v>
+        <v>554839</v>
       </c>
       <c r="B91" t="n">
         <v>2013</v>
@@ -5047,7 +5047,7 @@
         <v>2474</v>
       </c>
       <c r="D91" t="n">
-        <v>554839</v>
+        <v>2032</v>
       </c>
       <c r="E91" t="n">
         <v>1780</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2032</v>
+        <v>554832</v>
       </c>
       <c r="B92" t="n">
         <v>2013</v>
@@ -5098,7 +5098,7 @@
         <v>2474</v>
       </c>
       <c r="D92" t="n">
-        <v>554832</v>
+        <v>2032</v>
       </c>
       <c r="E92" t="n">
         <v>1772</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2032</v>
+        <v>554830</v>
       </c>
       <c r="B93" t="n">
         <v>2013</v>
@@ -5149,7 +5149,7 @@
         <v>2474</v>
       </c>
       <c r="D93" t="n">
-        <v>554830</v>
+        <v>2032</v>
       </c>
       <c r="E93" t="n">
         <v>1766</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2032</v>
+        <v>554835</v>
       </c>
       <c r="B94" t="n">
         <v>2013</v>
@@ -5200,7 +5200,7 @@
         <v>2474</v>
       </c>
       <c r="D94" t="n">
-        <v>554835</v>
+        <v>2032</v>
       </c>
       <c r="E94" t="n">
         <v>1783</v>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2032</v>
+        <v>554831</v>
       </c>
       <c r="B95" t="n">
         <v>2013</v>
@@ -5251,7 +5251,7 @@
         <v>2474</v>
       </c>
       <c r="D95" t="n">
-        <v>554831</v>
+        <v>2032</v>
       </c>
       <c r="E95" t="n">
         <v>1777</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2032</v>
+        <v>554833</v>
       </c>
       <c r="B96" t="n">
         <v>2013</v>
@@ -5302,7 +5302,7 @@
         <v>2474</v>
       </c>
       <c r="D96" t="n">
-        <v>554833</v>
+        <v>2032</v>
       </c>
       <c r="E96" t="n">
         <v>1779</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2032</v>
+        <v>554837</v>
       </c>
       <c r="B97" t="n">
         <v>2013</v>
@@ -5353,7 +5353,7 @@
         <v>2474</v>
       </c>
       <c r="D97" t="n">
-        <v>554837</v>
+        <v>2032</v>
       </c>
       <c r="E97" t="n">
         <v>4364</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2032</v>
+        <v>554836</v>
       </c>
       <c r="B98" t="n">
         <v>2013</v>
@@ -5404,7 +5404,7 @@
         <v>2474</v>
       </c>
       <c r="D98" t="n">
-        <v>554836</v>
+        <v>2032</v>
       </c>
       <c r="E98" t="n">
         <v>1767</v>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2032</v>
+        <v>554847</v>
       </c>
       <c r="B99" t="n">
         <v>2013</v>
@@ -5455,7 +5455,7 @@
         <v>2474</v>
       </c>
       <c r="D99" t="n">
-        <v>554847</v>
+        <v>2032</v>
       </c>
       <c r="E99" t="n">
         <v>4287</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2032</v>
+        <v>554849</v>
       </c>
       <c r="B100" t="n">
         <v>2013</v>
@@ -5506,7 +5506,7 @@
         <v>2474</v>
       </c>
       <c r="D100" t="n">
-        <v>554849</v>
+        <v>2032</v>
       </c>
       <c r="E100" t="n">
         <v>1782</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2032</v>
+        <v>554846</v>
       </c>
       <c r="B101" t="n">
         <v>2013</v>
@@ -5557,7 +5557,7 @@
         <v>2474</v>
       </c>
       <c r="D101" t="n">
-        <v>554846</v>
+        <v>2032</v>
       </c>
       <c r="E101" t="n">
         <v>4364</v>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2032</v>
+        <v>554848</v>
       </c>
       <c r="B102" t="n">
         <v>2013</v>
@@ -5608,7 +5608,7 @@
         <v>2474</v>
       </c>
       <c r="D102" t="n">
-        <v>554848</v>
+        <v>2032</v>
       </c>
       <c r="E102" t="n">
         <v>6685</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2032</v>
+        <v>554845</v>
       </c>
       <c r="B103" t="n">
         <v>2013</v>
@@ -5659,7 +5659,7 @@
         <v>2474</v>
       </c>
       <c r="D103" t="n">
-        <v>554845</v>
+        <v>2032</v>
       </c>
       <c r="E103" t="n">
         <v>6684</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2032</v>
+        <v>554840</v>
       </c>
       <c r="B104" t="n">
         <v>2013</v>
@@ -5710,7 +5710,7 @@
         <v>2474</v>
       </c>
       <c r="D104" t="n">
-        <v>554840</v>
+        <v>2032</v>
       </c>
       <c r="E104" t="n">
         <v>1768</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2032</v>
+        <v>554841</v>
       </c>
       <c r="B105" t="n">
         <v>2013</v>
@@ -5761,7 +5761,7 @@
         <v>2474</v>
       </c>
       <c r="D105" t="n">
-        <v>554841</v>
+        <v>2032</v>
       </c>
       <c r="E105" t="n">
         <v>1770</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2032</v>
+        <v>554844</v>
       </c>
       <c r="B106" t="n">
         <v>2013</v>
@@ -5812,7 +5812,7 @@
         <v>2474</v>
       </c>
       <c r="D106" t="n">
-        <v>554844</v>
+        <v>2032</v>
       </c>
       <c r="E106" t="n">
         <v>1765</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2032</v>
+        <v>554842</v>
       </c>
       <c r="B107" t="n">
         <v>2013</v>
@@ -5863,7 +5863,7 @@
         <v>2474</v>
       </c>
       <c r="D107" t="n">
-        <v>554842</v>
+        <v>2032</v>
       </c>
       <c r="E107" t="n">
         <v>1779</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2032</v>
+        <v>554843</v>
       </c>
       <c r="B108" t="n">
         <v>2013</v>
@@ -5914,7 +5914,7 @@
         <v>2474</v>
       </c>
       <c r="D108" t="n">
-        <v>554843</v>
+        <v>2032</v>
       </c>
       <c r="E108" t="n">
         <v>1771</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2032</v>
+        <v>554851</v>
       </c>
       <c r="B109" t="n">
         <v>2013</v>
@@ -5965,7 +5965,7 @@
         <v>2474</v>
       </c>
       <c r="D109" t="n">
-        <v>554851</v>
+        <v>2032</v>
       </c>
       <c r="E109" t="n">
         <v>1772</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2032</v>
+        <v>554858</v>
       </c>
       <c r="B110" t="n">
         <v>2013</v>
@@ -6016,7 +6016,7 @@
         <v>2474</v>
       </c>
       <c r="D110" t="n">
-        <v>554858</v>
+        <v>2032</v>
       </c>
       <c r="E110" t="n">
         <v>1780</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2032</v>
+        <v>554859</v>
       </c>
       <c r="B111" t="n">
         <v>2013</v>
@@ -6067,7 +6067,7 @@
         <v>2474</v>
       </c>
       <c r="D111" t="n">
-        <v>554859</v>
+        <v>2032</v>
       </c>
       <c r="E111" t="n">
         <v>1782</v>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2032</v>
+        <v>554853</v>
       </c>
       <c r="B112" t="n">
         <v>2013</v>
@@ -6118,7 +6118,7 @@
         <v>2474</v>
       </c>
       <c r="D112" t="n">
-        <v>554853</v>
+        <v>2032</v>
       </c>
       <c r="E112" t="n">
         <v>1771</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2032</v>
+        <v>554855</v>
       </c>
       <c r="B113" t="n">
         <v>2013</v>
@@ -6169,7 +6169,7 @@
         <v>2474</v>
       </c>
       <c r="D113" t="n">
-        <v>554855</v>
+        <v>2032</v>
       </c>
       <c r="E113" t="n">
         <v>6684</v>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2032</v>
+        <v>554852</v>
       </c>
       <c r="B114" t="n">
         <v>2013</v>
@@ -6220,7 +6220,7 @@
         <v>2474</v>
       </c>
       <c r="D114" t="n">
-        <v>554852</v>
+        <v>2032</v>
       </c>
       <c r="E114" t="n">
         <v>4241</v>
@@ -6262,7 +6262,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2032</v>
+        <v>554857</v>
       </c>
       <c r="B115" t="n">
         <v>2013</v>
@@ -6271,7 +6271,7 @@
         <v>2474</v>
       </c>
       <c r="D115" t="n">
-        <v>554857</v>
+        <v>2032</v>
       </c>
       <c r="E115" t="n">
         <v>6685</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2032</v>
+        <v>554850</v>
       </c>
       <c r="B116" t="n">
         <v>2013</v>
@@ -6322,7 +6322,7 @@
         <v>2474</v>
       </c>
       <c r="D116" t="n">
-        <v>554850</v>
+        <v>2032</v>
       </c>
       <c r="E116" t="n">
         <v>4286</v>
@@ -6364,7 +6364,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2032</v>
+        <v>554856</v>
       </c>
       <c r="B117" t="n">
         <v>2013</v>
@@ -6373,7 +6373,7 @@
         <v>2474</v>
       </c>
       <c r="D117" t="n">
-        <v>554856</v>
+        <v>2032</v>
       </c>
       <c r="E117" t="n">
         <v>1769</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2032</v>
+        <v>554854</v>
       </c>
       <c r="B118" t="n">
         <v>2013</v>
@@ -6424,7 +6424,7 @@
         <v>2474</v>
       </c>
       <c r="D118" t="n">
-        <v>554854</v>
+        <v>2032</v>
       </c>
       <c r="E118" t="n">
         <v>1783</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2032</v>
+        <v>554862</v>
       </c>
       <c r="B119" t="n">
         <v>2013</v>
@@ -6475,7 +6475,7 @@
         <v>2474</v>
       </c>
       <c r="D119" t="n">
-        <v>554862</v>
+        <v>2032</v>
       </c>
       <c r="E119" t="n">
         <v>1777</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2032</v>
+        <v>554863</v>
       </c>
       <c r="B120" t="n">
         <v>2013</v>
@@ -6526,7 +6526,7 @@
         <v>2474</v>
       </c>
       <c r="D120" t="n">
-        <v>554863</v>
+        <v>2032</v>
       </c>
       <c r="E120" t="n">
         <v>1770</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2032</v>
+        <v>554868</v>
       </c>
       <c r="B121" t="n">
         <v>2013</v>
@@ -6577,7 +6577,7 @@
         <v>2474</v>
       </c>
       <c r="D121" t="n">
-        <v>554868</v>
+        <v>2032</v>
       </c>
       <c r="E121" t="n">
         <v>4287</v>
@@ -6619,7 +6619,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2032</v>
+        <v>554869</v>
       </c>
       <c r="B122" t="n">
         <v>2013</v>
@@ -6628,7 +6628,7 @@
         <v>2474</v>
       </c>
       <c r="D122" t="n">
-        <v>554869</v>
+        <v>2032</v>
       </c>
       <c r="E122" t="n">
         <v>1776</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2032</v>
+        <v>554865</v>
       </c>
       <c r="B123" t="n">
         <v>2013</v>
@@ -6679,7 +6679,7 @@
         <v>2474</v>
       </c>
       <c r="D123" t="n">
-        <v>554865</v>
+        <v>2032</v>
       </c>
       <c r="E123" t="n">
         <v>1779</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2032</v>
+        <v>554867</v>
       </c>
       <c r="B124" t="n">
         <v>2013</v>
@@ -6730,7 +6730,7 @@
         <v>2474</v>
       </c>
       <c r="D124" t="n">
-        <v>554867</v>
+        <v>2032</v>
       </c>
       <c r="E124" t="n">
         <v>1767</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2032</v>
+        <v>554860</v>
       </c>
       <c r="B125" t="n">
         <v>2013</v>
@@ -6781,7 +6781,7 @@
         <v>2474</v>
       </c>
       <c r="D125" t="n">
-        <v>554860</v>
+        <v>2032</v>
       </c>
       <c r="E125" t="n">
         <v>1768</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2032</v>
+        <v>554864</v>
       </c>
       <c r="B126" t="n">
         <v>2013</v>
@@ -6832,7 +6832,7 @@
         <v>2474</v>
       </c>
       <c r="D126" t="n">
-        <v>554864</v>
+        <v>2032</v>
       </c>
       <c r="E126" t="n">
         <v>4286</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2032</v>
+        <v>554861</v>
       </c>
       <c r="B127" t="n">
         <v>2013</v>
@@ -6883,7 +6883,7 @@
         <v>2474</v>
       </c>
       <c r="D127" t="n">
-        <v>554861</v>
+        <v>2032</v>
       </c>
       <c r="E127" t="n">
         <v>1766</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2032</v>
+        <v>554866</v>
       </c>
       <c r="B128" t="n">
         <v>2013</v>
@@ -6934,7 +6934,7 @@
         <v>2474</v>
       </c>
       <c r="D128" t="n">
-        <v>554866</v>
+        <v>2032</v>
       </c>
       <c r="E128" t="n">
         <v>1765</v>
@@ -6976,7 +6976,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2032</v>
+        <v>554871</v>
       </c>
       <c r="B129" t="n">
         <v>2013</v>
@@ -6985,7 +6985,7 @@
         <v>2474</v>
       </c>
       <c r="D129" t="n">
-        <v>554871</v>
+        <v>2032</v>
       </c>
       <c r="E129" t="n">
         <v>1770</v>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2032</v>
+        <v>554877</v>
       </c>
       <c r="B130" t="n">
         <v>2013</v>
@@ -7036,7 +7036,7 @@
         <v>2474</v>
       </c>
       <c r="D130" t="n">
-        <v>554877</v>
+        <v>2032</v>
       </c>
       <c r="E130" t="n">
         <v>1769</v>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2032</v>
+        <v>554879</v>
       </c>
       <c r="B131" t="n">
         <v>2013</v>
@@ -7087,7 +7087,7 @@
         <v>2474</v>
       </c>
       <c r="D131" t="n">
-        <v>554879</v>
+        <v>2032</v>
       </c>
       <c r="E131" t="n">
         <v>1782</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2032</v>
+        <v>554870</v>
       </c>
       <c r="B132" t="n">
         <v>2013</v>
@@ -7138,7 +7138,7 @@
         <v>2474</v>
       </c>
       <c r="D132" t="n">
-        <v>554870</v>
+        <v>2032</v>
       </c>
       <c r="E132" t="n">
         <v>1768</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2032</v>
+        <v>554873</v>
       </c>
       <c r="B133" t="n">
         <v>2013</v>
@@ -7189,7 +7189,7 @@
         <v>2474</v>
       </c>
       <c r="D133" t="n">
-        <v>554873</v>
+        <v>2032</v>
       </c>
       <c r="E133" t="n">
         <v>1771</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2032</v>
+        <v>554874</v>
       </c>
       <c r="B134" t="n">
         <v>2013</v>
@@ -7240,7 +7240,7 @@
         <v>2474</v>
       </c>
       <c r="D134" t="n">
-        <v>554874</v>
+        <v>2032</v>
       </c>
       <c r="E134" t="n">
         <v>1783</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2032</v>
+        <v>554878</v>
       </c>
       <c r="B135" t="n">
         <v>2013</v>
@@ -7291,7 +7291,7 @@
         <v>2474</v>
       </c>
       <c r="D135" t="n">
-        <v>554878</v>
+        <v>2032</v>
       </c>
       <c r="E135" t="n">
         <v>1776</v>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2032</v>
+        <v>554872</v>
       </c>
       <c r="B136" t="n">
         <v>2013</v>
@@ -7342,7 +7342,7 @@
         <v>2474</v>
       </c>
       <c r="D136" t="n">
-        <v>554872</v>
+        <v>2032</v>
       </c>
       <c r="E136" t="n">
         <v>1772</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2032</v>
+        <v>554875</v>
       </c>
       <c r="B137" t="n">
         <v>2013</v>
@@ -7393,7 +7393,7 @@
         <v>2474</v>
       </c>
       <c r="D137" t="n">
-        <v>554875</v>
+        <v>2032</v>
       </c>
       <c r="E137" t="n">
         <v>6684</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2032</v>
+        <v>554876</v>
       </c>
       <c r="B138" t="n">
         <v>2013</v>
@@ -7444,7 +7444,7 @@
         <v>2474</v>
       </c>
       <c r="D138" t="n">
-        <v>554876</v>
+        <v>2032</v>
       </c>
       <c r="E138" t="n">
         <v>4364</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2032</v>
+        <v>554883</v>
       </c>
       <c r="B139" t="n">
         <v>2013</v>
@@ -7495,7 +7495,7 @@
         <v>2474</v>
       </c>
       <c r="D139" t="n">
-        <v>554883</v>
+        <v>2032</v>
       </c>
       <c r="E139" t="n">
         <v>4241</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2032</v>
+        <v>554884</v>
       </c>
       <c r="B140" t="n">
         <v>2013</v>
@@ -7546,7 +7546,7 @@
         <v>2474</v>
       </c>
       <c r="D140" t="n">
-        <v>554884</v>
+        <v>2032</v>
       </c>
       <c r="E140" t="n">
         <v>1765</v>
@@ -7588,7 +7588,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2032</v>
+        <v>554881</v>
       </c>
       <c r="B141" t="n">
         <v>2013</v>
@@ -7597,7 +7597,7 @@
         <v>2474</v>
       </c>
       <c r="D141" t="n">
-        <v>554881</v>
+        <v>2032</v>
       </c>
       <c r="E141" t="n">
         <v>1777</v>
@@ -7639,7 +7639,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2032</v>
+        <v>554880</v>
       </c>
       <c r="B142" t="n">
         <v>2013</v>
@@ -7648,7 +7648,7 @@
         <v>2474</v>
       </c>
       <c r="D142" t="n">
-        <v>554880</v>
+        <v>2032</v>
       </c>
       <c r="E142" t="n">
         <v>1766</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2032</v>
+        <v>554887</v>
       </c>
       <c r="B143" t="n">
         <v>2013</v>
@@ -7699,7 +7699,7 @@
         <v>2474</v>
       </c>
       <c r="D143" t="n">
-        <v>554887</v>
+        <v>2032</v>
       </c>
       <c r="E143" t="n">
         <v>4287</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2032</v>
+        <v>554882</v>
       </c>
       <c r="B144" t="n">
         <v>2013</v>
@@ -7750,7 +7750,7 @@
         <v>2474</v>
       </c>
       <c r="D144" t="n">
-        <v>554882</v>
+        <v>2032</v>
       </c>
       <c r="E144" t="n">
         <v>1779</v>
@@ -7792,7 +7792,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2032</v>
+        <v>554886</v>
       </c>
       <c r="B145" t="n">
         <v>2013</v>
@@ -7801,7 +7801,7 @@
         <v>2474</v>
       </c>
       <c r="D145" t="n">
-        <v>554886</v>
+        <v>2032</v>
       </c>
       <c r="E145" t="n">
         <v>4364</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2032</v>
+        <v>554888</v>
       </c>
       <c r="B146" t="n">
         <v>2013</v>
@@ -7852,7 +7852,7 @@
         <v>2474</v>
       </c>
       <c r="D146" t="n">
-        <v>554888</v>
+        <v>2032</v>
       </c>
       <c r="E146" t="n">
         <v>6685</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2032</v>
+        <v>554885</v>
       </c>
       <c r="B147" t="n">
         <v>2013</v>
@@ -7903,7 +7903,7 @@
         <v>2474</v>
       </c>
       <c r="D147" t="n">
-        <v>554885</v>
+        <v>2032</v>
       </c>
       <c r="E147" t="n">
         <v>1767</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2032</v>
+        <v>554889</v>
       </c>
       <c r="B148" t="n">
         <v>2013</v>
@@ -7954,7 +7954,7 @@
         <v>2474</v>
       </c>
       <c r="D148" t="n">
-        <v>554889</v>
+        <v>2032</v>
       </c>
       <c r="E148" t="n">
         <v>1780</v>
@@ -7996,7 +7996,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2032</v>
+        <v>554891</v>
       </c>
       <c r="B149" t="n">
         <v>2013</v>
@@ -8005,7 +8005,7 @@
         <v>2474</v>
       </c>
       <c r="D149" t="n">
-        <v>554891</v>
+        <v>2032</v>
       </c>
       <c r="E149" t="n">
         <v>1766</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2032</v>
+        <v>554897</v>
       </c>
       <c r="B150" t="n">
         <v>2013</v>
@@ -8054,7 +8054,7 @@
         <v>2474</v>
       </c>
       <c r="D150" t="n">
-        <v>554897</v>
+        <v>2032</v>
       </c>
       <c r="E150" t="n">
         <v>6684</v>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2032</v>
+        <v>554896</v>
       </c>
       <c r="B151" t="n">
         <v>2013</v>
@@ -8103,7 +8103,7 @@
         <v>2474</v>
       </c>
       <c r="D151" t="n">
-        <v>554896</v>
+        <v>2032</v>
       </c>
       <c r="E151" t="n">
         <v>1765</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2032</v>
+        <v>554898</v>
       </c>
       <c r="B152" t="n">
         <v>2013</v>
@@ -8152,7 +8152,7 @@
         <v>2474</v>
       </c>
       <c r="D152" t="n">
-        <v>554898</v>
+        <v>2032</v>
       </c>
       <c r="E152" t="n">
         <v>1769</v>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2032</v>
+        <v>554899</v>
       </c>
       <c r="B153" t="n">
         <v>2013</v>
@@ -8201,7 +8201,7 @@
         <v>2474</v>
       </c>
       <c r="D153" t="n">
-        <v>554899</v>
+        <v>2032</v>
       </c>
       <c r="E153" t="n">
         <v>6685</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2032</v>
+        <v>554892</v>
       </c>
       <c r="B154" t="n">
         <v>2013</v>
@@ -8250,7 +8250,7 @@
         <v>2474</v>
       </c>
       <c r="D154" t="n">
-        <v>554892</v>
+        <v>2032</v>
       </c>
       <c r="E154" t="n">
         <v>1777</v>
@@ -8290,7 +8290,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2032</v>
+        <v>554893</v>
       </c>
       <c r="B155" t="n">
         <v>2013</v>
@@ -8299,7 +8299,7 @@
         <v>2474</v>
       </c>
       <c r="D155" t="n">
-        <v>554893</v>
+        <v>2032</v>
       </c>
       <c r="E155" t="n">
         <v>1770</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2032</v>
+        <v>554894</v>
       </c>
       <c r="B156" t="n">
         <v>2013</v>
@@ -8348,7 +8348,7 @@
         <v>2474</v>
       </c>
       <c r="D156" t="n">
-        <v>554894</v>
+        <v>2032</v>
       </c>
       <c r="E156" t="n">
         <v>4286</v>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2032</v>
+        <v>554895</v>
       </c>
       <c r="B157" t="n">
         <v>2013</v>
@@ -8397,7 +8397,7 @@
         <v>2474</v>
       </c>
       <c r="D157" t="n">
-        <v>554895</v>
+        <v>2032</v>
       </c>
       <c r="E157" t="n">
         <v>1772</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2032</v>
+        <v>554890</v>
       </c>
       <c r="B158" t="n">
         <v>2013</v>
@@ -8446,7 +8446,7 @@
         <v>2474</v>
       </c>
       <c r="D158" t="n">
-        <v>554890</v>
+        <v>2032</v>
       </c>
       <c r="E158" t="n">
         <v>1768</v>
@@ -8486,7 +8486,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2032</v>
+        <v>554907</v>
       </c>
       <c r="B159" t="n">
         <v>2013</v>
@@ -8495,7 +8495,7 @@
         <v>2474</v>
       </c>
       <c r="D159" t="n">
-        <v>554907</v>
+        <v>2032</v>
       </c>
       <c r="E159" t="n">
         <v>1776</v>
@@ -8535,7 +8535,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2032</v>
+        <v>554909</v>
       </c>
       <c r="B160" t="n">
         <v>2013</v>
@@ -8544,7 +8544,7 @@
         <v>2474</v>
       </c>
       <c r="D160" t="n">
-        <v>554909</v>
+        <v>2032</v>
       </c>
       <c r="E160" t="n">
         <v>1782</v>
@@ -8584,7 +8584,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2032</v>
+        <v>554904</v>
       </c>
       <c r="B161" t="n">
         <v>2013</v>
@@ -8593,7 +8593,7 @@
         <v>2474</v>
       </c>
       <c r="D161" t="n">
-        <v>554904</v>
+        <v>2032</v>
       </c>
       <c r="E161" t="n">
         <v>1767</v>
@@ -8633,7 +8633,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2032</v>
+        <v>554905</v>
       </c>
       <c r="B162" t="n">
         <v>2013</v>
@@ -8642,7 +8642,7 @@
         <v>2474</v>
       </c>
       <c r="D162" t="n">
-        <v>554905</v>
+        <v>2032</v>
       </c>
       <c r="E162" t="n">
         <v>4364</v>
@@ -8682,7 +8682,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2032</v>
+        <v>554903</v>
       </c>
       <c r="B163" t="n">
         <v>2013</v>
@@ -8691,7 +8691,7 @@
         <v>2474</v>
       </c>
       <c r="D163" t="n">
-        <v>554903</v>
+        <v>2032</v>
       </c>
       <c r="E163" t="n">
         <v>1783</v>
@@ -8731,7 +8731,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2032</v>
+        <v>554902</v>
       </c>
       <c r="B164" t="n">
         <v>2013</v>
@@ -8740,7 +8740,7 @@
         <v>2474</v>
       </c>
       <c r="D164" t="n">
-        <v>554902</v>
+        <v>2032</v>
       </c>
       <c r="E164" t="n">
         <v>1771</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2032</v>
+        <v>554906</v>
       </c>
       <c r="B165" t="n">
         <v>2013</v>
@@ -8789,7 +8789,7 @@
         <v>2474</v>
       </c>
       <c r="D165" t="n">
-        <v>554906</v>
+        <v>2032</v>
       </c>
       <c r="E165" t="n">
         <v>4287</v>
@@ -8829,7 +8829,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2032</v>
+        <v>554900</v>
       </c>
       <c r="B166" t="n">
         <v>2013</v>
@@ -8838,7 +8838,7 @@
         <v>2474</v>
       </c>
       <c r="D166" t="n">
-        <v>554900</v>
+        <v>2032</v>
       </c>
       <c r="E166" t="n">
         <v>1779</v>
@@ -8878,7 +8878,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2032</v>
+        <v>554908</v>
       </c>
       <c r="B167" t="n">
         <v>2013</v>
@@ -8887,7 +8887,7 @@
         <v>2474</v>
       </c>
       <c r="D167" t="n">
-        <v>554908</v>
+        <v>2032</v>
       </c>
       <c r="E167" t="n">
         <v>1780</v>
@@ -8927,7 +8927,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2032</v>
+        <v>554901</v>
       </c>
       <c r="B168" t="n">
         <v>2013</v>
@@ -8936,7 +8936,7 @@
         <v>2474</v>
       </c>
       <c r="D168" t="n">
-        <v>554901</v>
+        <v>2032</v>
       </c>
       <c r="E168" t="n">
         <v>4241</v>
@@ -8976,7 +8976,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2032</v>
+        <v>554910</v>
       </c>
       <c r="B169" t="n">
         <v>2013</v>
@@ -8985,7 +8985,7 @@
         <v>2474</v>
       </c>
       <c r="D169" t="n">
-        <v>554910</v>
+        <v>2032</v>
       </c>
       <c r="E169" t="n">
         <v>1768</v>
@@ -9025,7 +9025,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2032</v>
+        <v>554914</v>
       </c>
       <c r="B170" t="n">
         <v>2013</v>
@@ -9034,7 +9034,7 @@
         <v>2474</v>
       </c>
       <c r="D170" t="n">
-        <v>554914</v>
+        <v>2032</v>
       </c>
       <c r="E170" t="n">
         <v>1783</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2032</v>
+        <v>554911</v>
       </c>
       <c r="B171" t="n">
         <v>2013</v>
@@ -9083,7 +9083,7 @@
         <v>2474</v>
       </c>
       <c r="D171" t="n">
-        <v>554911</v>
+        <v>2032</v>
       </c>
       <c r="E171" t="n">
         <v>1777</v>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2032</v>
+        <v>554915</v>
       </c>
       <c r="B172" t="n">
         <v>2013</v>
@@ -9132,7 +9132,7 @@
         <v>2474</v>
       </c>
       <c r="D172" t="n">
-        <v>554915</v>
+        <v>2032</v>
       </c>
       <c r="E172" t="n">
         <v>1767</v>
@@ -9172,7 +9172,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2032</v>
+        <v>554918</v>
       </c>
       <c r="B173" t="n">
         <v>2013</v>
@@ -9181,7 +9181,7 @@
         <v>2474</v>
       </c>
       <c r="D173" t="n">
-        <v>554918</v>
+        <v>2032</v>
       </c>
       <c r="E173" t="n">
         <v>6685</v>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2032</v>
+        <v>554912</v>
       </c>
       <c r="B174" t="n">
         <v>2013</v>
@@ -9230,7 +9230,7 @@
         <v>2474</v>
       </c>
       <c r="D174" t="n">
-        <v>554912</v>
+        <v>2032</v>
       </c>
       <c r="E174" t="n">
         <v>4286</v>
@@ -9270,7 +9270,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2032</v>
+        <v>554916</v>
       </c>
       <c r="B175" t="n">
         <v>2013</v>
@@ -9279,7 +9279,7 @@
         <v>2474</v>
       </c>
       <c r="D175" t="n">
-        <v>554916</v>
+        <v>2032</v>
       </c>
       <c r="E175" t="n">
         <v>1769</v>
@@ -9319,7 +9319,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2032</v>
+        <v>554919</v>
       </c>
       <c r="B176" t="n">
         <v>2013</v>
@@ -9328,7 +9328,7 @@
         <v>2474</v>
       </c>
       <c r="D176" t="n">
-        <v>554919</v>
+        <v>2032</v>
       </c>
       <c r="E176" t="n">
         <v>1780</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2032</v>
+        <v>554913</v>
       </c>
       <c r="B177" t="n">
         <v>2013</v>
@@ -9377,7 +9377,7 @@
         <v>2474</v>
       </c>
       <c r="D177" t="n">
-        <v>554913</v>
+        <v>2032</v>
       </c>
       <c r="E177" t="n">
         <v>1771</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2032</v>
+        <v>554917</v>
       </c>
       <c r="B178" t="n">
         <v>2013</v>
@@ -9426,7 +9426,7 @@
         <v>2474</v>
       </c>
       <c r="D178" t="n">
-        <v>554917</v>
+        <v>2032</v>
       </c>
       <c r="E178" t="n">
         <v>4287</v>
@@ -9462,6 +9462,253 @@
       </c>
       <c r="O178" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>554921</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1770</v>
+      </c>
+      <c r="F179" t="n">
+        <v>6685</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" s="1" t="n">
+        <v>46219.9375</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>19</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>2</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>554929</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1782</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" s="1" t="n">
+        <v>46219.9375</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>19</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>554770</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1777</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1772</v>
+      </c>
+      <c r="G181" t="n">
+        <v>75722</v>
+      </c>
+      <c r="H181" s="1" t="n">
+        <v>46220.9375</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>2</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>554925</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1765</v>
+      </c>
+      <c r="F182" t="n">
+        <v>4286</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" s="1" t="n">
+        <v>46220.95833333334</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>19</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>554927</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E183" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" s="1" t="n">
+        <v>46220.95833333334</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>19</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="n">
+        <v>2</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/tabela_partidas_tratada.xlsx
+++ b/data/processed/tabela_partidas_tratada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O183"/>
+  <dimension ref="A1:O206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9711,6 +9711,1143 @@
         <v>1</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>554920</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1766</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1777</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" s="1" t="n">
+        <v>46224.9375</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>19</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>554924</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4241</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" s="1" t="n">
+        <v>46225.9375</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>19</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>554922</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1772</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1783</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" s="1" t="n">
+        <v>46226.02083333334</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>19</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>2</v>
+      </c>
+      <c r="O186" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>554926</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E187" t="n">
+        <v>6684</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1771</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" s="1" t="n">
+        <v>46226.02083333334</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>19</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>554928</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1776</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1768</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" s="1" t="n">
+        <v>46226.02083333334</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>19</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>554771</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1770</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1782</v>
+      </c>
+      <c r="G189" t="n">
+        <v>19023</v>
+      </c>
+      <c r="H189" s="1" t="n">
+        <v>46226.9375</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>4</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>554923</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1779</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4287</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" s="1" t="n">
+        <v>46226.9375</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>19</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="n">
+        <v>3</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>554930</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6684</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" s="1" t="n">
+        <v>46228.89583333334</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>20</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>2</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>554938</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E192" t="n">
+        <v>6685</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1772</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" s="1" t="n">
+        <v>46228.89583333334</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>20</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>554939</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4364</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" s="1" t="n">
+        <v>46228.97916666666</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>20</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>554931</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1777</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1779</v>
+      </c>
+      <c r="G194" t="n">
+        <v>18754</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>46229.79166666666</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>20</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>554933</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1771</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" s="1" t="n">
+        <v>46229.79166666666</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>20</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>1</v>
+      </c>
+      <c r="O195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>554932</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E196" t="n">
+        <v>4286</v>
+      </c>
+      <c r="F196" t="n">
+        <v>4241</v>
+      </c>
+      <c r="G196" t="n">
+        <v>60911</v>
+      </c>
+      <c r="H196" s="1" t="n">
+        <v>46229.89583333334</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>20</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>554934</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1783</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1776</v>
+      </c>
+      <c r="G197" t="n">
+        <v>11161</v>
+      </c>
+      <c r="H197" s="1" t="n">
+        <v>46229.89583333334</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>20</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>554935</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1767</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1765</v>
+      </c>
+      <c r="G198" t="n">
+        <v>60939</v>
+      </c>
+      <c r="H198" s="1" t="n">
+        <v>46229.89583333334</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>20</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>554936</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1769</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1766</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" s="1" t="n">
+        <v>46229.9375</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>20</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>554937</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E200" t="n">
+        <v>4287</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1782</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" s="1" t="n">
+        <v>46229.9375</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>20</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>2</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>554946</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E201" t="n">
+        <v>6684</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1783</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" s="1" t="n">
+        <v>46232.9375</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>21</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>554947</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E202" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F202" t="n">
+        <v>4287</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" s="1" t="n">
+        <v>46232.9375</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>21</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>MANDANTE</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>2</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>554945</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1765</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1777</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" s="1" t="n">
+        <v>46233.02083333334</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>21</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>554949</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C204" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1782</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" s="1" t="n">
+        <v>46233.02083333334</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>21</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>554943</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1779</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1768</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" s="1" t="n">
+        <v>46233.9375</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>21</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>554944</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2032</v>
+      </c>
+      <c r="E206" t="n">
+        <v>4241</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1771</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" s="1" t="n">
+        <v>46234.02083333334</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>21</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>VISITANTE</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
